--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -709,25 +709,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -784,21 +775,16 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -855,21 +841,16 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -908,25 +889,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -983,25 +955,21 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>1 IBT (unit 2)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1040,23 +1008,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1105,25 +1066,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1162,25 +1114,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1219,25 +1162,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1276,29 +1210,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>KTT ITP 220 MVA</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1337,25 +1263,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1412,25 +1329,21 @@
       <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>2 IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1469,25 +1382,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1526,29 +1430,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>KTT Aspek 40 MVA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1605,25 +1501,21 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1662,25 +1554,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1719,29 +1602,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>KTT Sucofindo 40 MVA</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1780,29 +1655,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1841,25 +1708,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1898,23 +1756,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>T/L bay single phi arah Bogor Baru &amp; Cibadak Baru</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1963,19 +1814,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2024,19 +1867,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2085,29 +1920,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>KTT Cemindo 70 MVA</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2146,19 +1973,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2207,25 +2026,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2264,19 +2074,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2325,25 +2127,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2382,25 +2175,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2457,25 +2241,21 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2514,25 +2294,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2571,25 +2342,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2628,25 +2390,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2685,23 +2438,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>GI simpul; trafo &gt;70%</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2750,19 +2496,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2811,19 +2549,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2872,25 +2602,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2929,25 +2650,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2986,25 +2698,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3043,25 +2746,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3100,25 +2794,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3157,17 +2842,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): CNJUR : - / CGRLG : Trf 9,10</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3183,7 +2862,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3222,17 +2900,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): LGDAR Trf 1,2,3,4</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3248,7 +2920,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3365,7 +3036,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Semen Baru</t>
@@ -3386,7 +3056,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -3400,8 +3069,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3428,7 +3095,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Cimanggis</t>
@@ -3449,7 +3115,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -3463,8 +3128,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3516,7 +3179,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -3530,8 +3192,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3558,7 +3218,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Gandaria</t>
@@ -3579,7 +3238,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -3593,8 +3251,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3621,7 +3277,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Depok Baru</t>
@@ -3642,7 +3297,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -3656,8 +3310,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3684,7 +3336,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Depok - Depok Baru</t>
@@ -3705,7 +3356,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -3719,8 +3369,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3747,7 +3395,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Semen Baru - ITP</t>
@@ -3768,7 +3415,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3782,8 +3428,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3835,7 +3479,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3849,8 +3492,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3902,7 +3543,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3916,8 +3556,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3944,7 +3582,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT 70 kV Cibinong - Cileungsi</t>
@@ -3965,7 +3602,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -3979,8 +3615,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4007,7 +3641,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT 70 kV Semen Baru - Semen Mas</t>
@@ -4028,7 +3661,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -4042,8 +3674,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4070,7 +3700,6 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Outlet PLTP Salak Lama 1,2,3</t>
@@ -4091,7 +3720,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -4105,8 +3733,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4133,7 +3759,6 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Outlet PLTP Salak Lama Binary</t>
@@ -4154,7 +3779,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -4168,8 +3792,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4196,7 +3818,6 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Outlet PLTP Salak Baru 4,5,6</t>
@@ -4217,7 +3838,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -4231,8 +3851,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4259,7 +3877,6 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Outlet PLTU Pelabuhan Ratu 1,2,3</t>
@@ -4280,7 +3897,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
       </c>
@@ -4294,8 +3910,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4322,7 +3936,6 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Salak - Salak Baru</t>
@@ -4343,7 +3956,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -4357,8 +3969,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4410,7 +4020,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -4424,8 +4033,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4477,7 +4084,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -4491,8 +4097,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4544,7 +4148,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -4558,8 +4161,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4611,7 +4212,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -4625,8 +4225,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4678,7 +4276,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -4692,8 +4289,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4720,7 +4315,6 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Pelabuhan Ratu - Bayah</t>
@@ -4741,7 +4335,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -4755,8 +4348,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4783,7 +4374,6 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Pelabuhan Ratu - Mping</t>
@@ -4804,7 +4394,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4818,8 +4407,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4846,7 +4433,6 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT Pelabuhan Ratu - Jampang</t>
@@ -4867,7 +4453,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -4881,8 +4466,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4909,7 +4492,6 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT Cibadak Baru - Ciawi</t>
@@ -4930,7 +4512,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -4944,8 +4525,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4997,7 +4576,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -5011,8 +4589,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5039,7 +4615,6 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>SUTT Katulampa - Cugenang (arah UP2B Jabar)</t>
@@ -5060,7 +4635,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -5074,8 +4648,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5102,7 +4674,6 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTT Lembur Situ - Lengkong Dar (arah UP2B Jabar)</t>
@@ -5123,7 +4694,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -5137,8 +4707,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5165,7 +4733,6 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>Outlet PLTA Ubrug 1,2,3</t>
@@ -5186,7 +4753,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -5200,8 +4766,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5228,7 +4792,6 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>SUTT 70 kV Cibadak - Ubrug</t>
@@ -5249,7 +4812,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -5263,8 +4825,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5291,7 +4851,6 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTT 70 kV Ubrug - Pelabuhan Ratu</t>
@@ -5312,7 +4871,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -5326,8 +4884,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5435,7 +4991,6 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -5449,7 +5004,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>CIBINONG</t>
@@ -5523,22 +5077,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] GI 150 kV Bogor Baru merupakan GI Simpul yang apabila terjadi gangguan Busbar dapat mengakibatlkan terpisahnya IBT Cibinong, IBT Depok dan Komplek Pembangkitan Salak dan Pelabuhan Ratu sehingga berdampak sebagian beban padam pada Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2-Depok 2</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Bogor Baru merupakan GI Simpul yang apabila terjadi gangguan Busbar dapat mengakibatlkan terpisahnya IBT Cibinong, IBT Depok dan Komplek Pembangkitan Salak dan Pelabuhan Ratu sehingga berdampak sebagian beban padam pada Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2 -Depok 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Terjadi beban padam akibat hilang Tegangan pada Sebagian Subsistem Pelabuhan Ratu - Salak-Cibinong 1,2 - Depok 2 sebesar 713 MW. 2.Kehilangan pasokan pembangkit PLTU Pelabuhan Ratu 3 Unit sebesar 960 MW dan PLTP Salak 6 Unit 380 MW. 3.Kesulitan dalam penjadwalan pemeliharaan Busbar pada GI 150 kV Bogor Baru</t>
+          <t>1. Terjadi beban padam akibat hilang Tegangan pada Sebagian Subsistem Pelabuhan Ratu - Salak -Cibinong 1,2 - Depok 2 sebesar 713 MW. 2. Kehilangan pasokan pembangkit PLTU Pelabuhan Ratu 3 Unit sebesar 960 MW dan PLTP Salak 6 Unit 380 MW. 3. Kesulitan dalam penjadwalan pemeliharaan Busbar pada GI 150 kV Bogor Baru</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Telah terpasang OFGS dengan target 6 Unit PLTP Salak. 2.Pengaturan pembebanan Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2 - Depok 2 agar pembebanan ruas SUTT Bogor -Sentul - Cibinong sebesar 150 MW- 500 A. 3.Rekonfigurasi subsistem Pelabuhan Ratu - Salak - Cibinong 1,2-Depok 2 saat PLTU Pelabuhan Ratu operasi 3 Unit adalah: a) Memasok Subsistem Bandung Selatan sampai GI 150 kV Cianjur (1 trafo) b) Memasok Susbsistem Cilegon sampai GI 150 kV Saketi (GI 150 kV Bayah , GI 150 kV Malingping (1 trafo), GI 150 kV Saketi (3 trafo) 4.Pemeliharaan Busbar saat periode beban rendah dan menyesuaikan PO PLTU Pelabuhan Ratu</t>
+          <t>1. Telah terpasang OFGS dengan target 6 Unit PLTP Salak. 2. Pengaturan pembebanan Subsistem Pelabuhan Ratu - Salak - Cibinong 1,2 - Depok 2 agar pembebanan ruas SUTT Bogor -Sentul - Cibinong sebesar 150 MW - 500 A. 3. Rekonfigurasi subsistem Pelabuhan Ratu - Salak - Cibinong 1,2 -Depok 2 saat PLTU Pelabuhan Ratu operasi 3 Unit adalah : a) Memasok Subsistem Bandung Selatan sampai GI 150 kV Cianjur (1 trafo) b) Memasok Susbsistem Cilegon sampai GI 150 kV Saketi (GI 150 kV Bayah , GI 150 kV Malingping (1 trafo), GI 150 kV Saketi (3 trafo) 4. Pemeliharaan Busbar saat periode beban rendah dan menyesuaikan PO PLTU Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Usulan penambahan Bus Section dan kopel kedua pada GI 150 kV Bogor Baru. diusulkan COD Tahun 2027. 2.Percepatan Pembangunan GITET Ubrug atau GITET Citereup beserta outlet terkait. Sesuai RUPTL 2025 - 2034, COD Tahun 2028 (diusulkan dipercepat Tahun 2026)</t>
+          <t>Jangka Pendek : 1. Usulan penambahan Bus Section dan kopel kedua pada GI 150 kV Bogor Baru. diusulkan COD Tahun 2027. 2. Percepatan Pembangunan GITET Ubrug atau GITET Citereup beserta outlet terkait. Sesuai RUPTL 2025 - 2034, COD Tahun 2028 (diusulkan dipercepat Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -5558,17 +5112,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] 1.KonfigurasiSingle Phidi GIS Salak Baru T/L Bay 150 kV arah Bogor baru dan T/L Bay Cibadak baru berkapasitas 1600 A per Sirkit dan sudah berbeban diatas 50% (855 A) sehingga tidak memenuhi kriteria N-1. 2.Apabila pada ruas tersebut terjadi gangguan trip 1 sirkit atau keluar karena pemeliharaan maka outlet tersebut terjadi Overload (N-1 tidak terpenuhi) sehingga harus mengurangi Pasokan dari PLTP Salak</t>
+          <t>[N-1] 1.Konfigurasi Single Phi di GIS Salak Baru T/L Bay 150 kV arah Bogor baru dan T/L Bay Cibadak baru berkapasitas 1600 A per Sirkit dan sudah berbeban diatas 50% (855 A) sehingga tidak memenuhi kriteria N-1. 2.Apabila pada ruas tersebut terjadi gangguan trip 1 sirkit atau keluar karena pemeliharaan maka outlet tersebut terjadi Overload (N-1 tidak terpenuhi) sehingga harus mengurangi Pasokan dari PLTP Salak</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload pada SUTT 150 kV Salak Baru-Bogor Baru atau SUTT 150 kV Salak Baru- Cibadak Baru apabila trip 1 sirkit pada salah satu ruas tersebut. 2.Kesulitan dalam pemeliharaan SUTT</t>
+          <t>1. Terjadi Overload pada SUTT 150 kV Salak Baru-Bogor Baru atau SUTT 150 kV Salak Baru- Cibadak Baru apabila trip 1 sirkit pada salah satu ruas tersebut. 2. Kesulitan dalam pemeliharaan SUTT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Pengaturan pembebanan Pembangkit Salak dari 380 MW menjadi 330 MW apabila ada pekerjaan/gangguan 1 sirkit pada ruas tersebut. 2.Rencana akan di implementasikan skema OGS di SUTT 150 kV Salak Baru-Bogor Baru &amp; Salak Baru-Cibadak Baru dengan target 1 Unit PLTP Salak Lama (57 MW)</t>
+          <t>1. Pengaturan pembebanan Pembangkit Salak dari 380 MW menjadi 330 MW apabila ada pekerjaan/gangguan 1 sirkit pada ruas tersebut. 2. Rencana akan di implementasikan skema OGS di SUTT 150 kV Salak Baru-Bogor Baru &amp; Salak Baru-Cibadak Baru dengan target 1 Unit PLTP Salak Lama (57 MW)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5633,17 +5187,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Kesulitan dalam melakukan pekerjaan ruas SUTT 150 kV Pratu- Cibadak jika Kit Pratu Operasi Maksimum 3 Unit. 2.Potensi Overload pada ruas SUTT 150 kV Bogor Baru- Cianjur dan Bogor Baru-Katulampa- Cianjur jika terjadi N-2 Pratu-Cibadak Baru</t>
+          <t>1.Kesulitan dalam melakukan pekerjaan ruas SUTT 150 kV Pratu - Cibadak jika Kit Pratu Operasi Maksimum 3 Unit. 2.Potensi Overload pada ruas SUTT 150 kV Bogor Baru- Cianjur dan Bogor Baru-Katulampa- Cianjur jika terjadi N-2 Pratu-Cibadak Baru</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Pekerjaan padam Ruas Pratu-Cibadak Baru dilakukan ketika Kit Pratu Operasi 2 Unit (600 MW). 2.Sudah terpasang skema Defense Scheme OGS pada ruas Bogor Baru-Cianjur dan Bogor Baru- Katulampa-Cianjur</t>
+          <t>1. Pekerjaan padam Ruas Pratu-Cibadak Baru dilakukan ketika Kit Pratu Operasi 2 Unit (600 MW). 2. Sudah terpasang skema Defense Scheme OGS pada ruas Bogor Baru-Cianjur dan Bogor Baru- Katulampa-Cianjur</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek : Rekonduktoringdandouble phiruas Bogor Baru-Katulampa-Cianjur dan Bogor Baru-Cianjur menjadi ACSR 2xDove, RUPTL 2025-2034 COD di Tahun 2027</t>
+          <t>Jangka Pendek : Rekonduktoring dan double phi ruas Bogor Baru-Katulampa-Cianjur dan Bogor Baru-Cianjur menjadi ACSR 2xDove, RUPTL 2025 -2034 COD di Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5227,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rekonfigurasi pada Subsistem Pelabuhan ratu - Salak - Cibinong 1,2-Depok 2</t>
+          <t>Rekonfigurasi pada Subsistem Pelabuhan ratu - Salak - Cibinong 1,2 -Depok 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek : Percepatan Pembangunan GITET Ubrug atau GITET Citereup beserta outlet terkait.Sesuai RUPTL 2023- 2032, COD Tahun 2028 (diusulkan dipercepat Tahun 2026)</t>
+          <t>Jangka Pendek : Percepatan Pembangunan GITET Ubrug atau GITET Citereup beserta outlet terkait. Sesuai RUPTL 2023 - 2032, COD Tahun 2028 (diusulkan dipercepat Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5267,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek : Pembangunan GI 150 kV Sentul Baru, sesuai RUPTL Tahun 2025- 2034 COD Tahun 2025.GI dan SUTT terkait sudah terkontrak</t>
+          <t>Jangka Pendek : Pembangunan GI 150 kV Sentul Baru, sesuai RUPTL Tahun 2025- 2034 COD Tahun 2025. GI dan SUTT terkait sudah terkontrak</t>
         </is>
       </c>
     </row>
@@ -5733,22 +5287,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-2] Terjadi ketidakstabilan kit pratu saat terjadi N- 2SUTT 150 kVPratu - CibadakBaru</t>
+          <t>[N-2] Terjadi ketidakstabilan kit pratu saat terjadi N- 2 SUTT 150 kVPratu - Cibadak Baru</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terjadi fenomena swing dan mengakibatkan Semua unit KitPratu out of step atau trip dan menyebabkan Dampak OLS IBT Cibinong bekerja</t>
+          <t>Terjadi fenomena swing dan mengakibatkan Semua unit Kit Pratu out of step atau trip dan menyebabkan Dampak OLS IBT Cibinong bekerja</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Penjadwalan SUTT dilakukan saat periode pemeliharaan unit Kit pratu. Pengaturan pola operasiKit pratu maks 550 MWsaat pekerjaan SUTT 150 kVPratu -CibadakBaru. Mitigasi PemasanganreleOGSSUTT 150 kVPratu - CibadakBarudengantarget 1 unit 1 Kit Pratu</t>
+          <t>Penjadwalan SUTT dilakukan saat periode pemeliharaan unit Kit pratu. Pengaturan pola operasi Kit pratu maks 550 MW saat pekerjaan SUTT 150 kVPratu -Cibadak Baru. Mitigasi Pemasangan rele OGSSUTT 150 kVPratu - Cibadak Barudengantarget 1 unit 1 Kit Pratu</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Menengah : Usulan pembangunan GITET 500/150 kV Ubrug berikut outletnya (Tx. Pratu-Cibadak Baru 1,2 dan Pratu-Semen Jawa 1,2 untuk 150 kV dan untuk 500 kV Tx. Depok- Tasik). Diusulkan COD Tahun 2029</t>
+          <t>Jangka Menengah : Usulan pembangunan GITET 500/150 kV Ubrug berikut outletnya (Tx. Pratu-Cibadak Baru 1,2 dan Pratu -Semen Jawa 1,2 untuk 150 kV dan untuk 500 kV Tx. Depok- Tasik). Diusulkan COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5332,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.Penjadwalan SUTT dilakukan saat periode pemeliharaan unit Kit pratu. 2.Pengaturan pola operasiKit pratu maks 550 MWsaat pekerjaan SUTT 150 kVPratu-CibadakBaru. 3.PemasanganreleOGSSUTT 150 kVPratu - CibadakBarudengantarget 1 unit 1 Kit Pratu</t>
+          <t>1. Penjadwalan SUTT dilakukan saat periode pemeliharaan unit Kit pratu. 2. Pengaturan pola operasi Kit pratu maks 550 MW saat pekerjaan SUTT 150 kV Pratu-CibadakBaru. 3. PemasanganreleOGSSUTT 150 kVPratu - Cibadak Barudengantarget 1 unit 1 Kit Pratu</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Pembangunan GI 150 kV Sentul Baru, sesuai RUPTL Tahun 2025- 2034 COD Tahun 2025. GI dan SUTT terkait sudah terkontrak. Jangka Menengah : 2.Usulan Uprating SUTT Pratu- Lembur Situ-Semen jawa menjadi 3000 A, diusulkan COD Tahun 2029. 3.Usulan pembangunan GITET 500/150 kV Ubrug berikut outletnya (Tx. Pratu-Cibadak Baru 1,2 dan Pratu-Semen Jawa 1,2 untuk 150 kV dan untuk 500 kV Tx. Depok-Tasik), diusulkan COD Tahun 2029</t>
+          <t>Jangka Pendek : 1. Pembangunan GI 150 kV Sentul Baru, sesuai RUPTL Tahun 2025- 2034 COD Tahun 2025. GI dan SUTT terkait sudah terkontrak. Jangka Menengah : 2. Usulan Uprating SUTT Pratu- Lembur Situ-Semen jawa menjadi 3000 A, diusulkan COD Tahun 2029. 3. Usulan pembangunan GITET 500/150 kV Ubrug berikut outletnya (Tx. Pratu-Cibadak Baru 1,2 dan Pratu -Semen Jawa 1,2 untuk 150 kV dan untuk 500 kV Tx. Depok-Tasik), diusulkan COD Tahun 2029</t>
         </is>
       </c>
     </row>

--- a/samples/ss_plbratu_ingest.xlsx
+++ b/samples/ss_plbratu_ingest.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,21 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GABUNGAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gabungan kedua sisi</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>101</v>
       </c>
     </row>
